--- a/database/seeders/xlsx/2.xlsx
+++ b/database/seeders/xlsx/2.xlsx
@@ -1,20 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="82">
   <si>
     <t>subcategory_id</t>
   </si>
@@ -73,184 +86,211 @@
     <t>Mr.Green</t>
   </si>
   <si>
+    <t>Средство для мытья посуды MR.GREEN Алоэ Вера</t>
+  </si>
+  <si>
     <t>Средство для мытья посуды MR.GREEN Алоэ Вера 500 мл</t>
   </si>
   <si>
+    <t>Гелеобразный нейтральный концентрат умеренной пенности...</t>
+  </si>
+  <si>
+    <t>/storage/products/67.png</t>
+  </si>
+  <si>
+    <t>500 мл</t>
+  </si>
+  <si>
+    <t>Средство для мытья посуды MR.GREEN Арбуз</t>
+  </si>
+  <si>
     <t>Средство для мытья посуды MR.GREEN Арбуз 500 мл</t>
   </si>
   <si>
+    <t>/storage/products/68.png</t>
+  </si>
+  <si>
     <t>Средство для мытья посуды MR.GREEN Яблоко 500 мл</t>
   </si>
   <si>
+    <t>/storage/products/69.png</t>
+  </si>
+  <si>
     <t>Средство для мытья посуды MR.GREEN Лимон 500 мл</t>
   </si>
   <si>
+    <t>/storage/products/70.png</t>
+  </si>
+  <si>
     <t>Средство для мытья посуды MR.GREEN Гранат 500 мл</t>
   </si>
   <si>
+    <t>/storage/products/71.png</t>
+  </si>
+  <si>
     <t>Средство для мытья посуды MR.GREEN Лайм-Мята 500 мл</t>
   </si>
   <si>
+    <t>/storage/products/72.png</t>
+  </si>
+  <si>
     <t>MR.GREEN 'POWER' АНТИЖИР PROFESSIONAL 500 мл</t>
   </si>
   <si>
+    <t>Жидкий сильнощелочной концентрат для очистки от нагара...</t>
+  </si>
+  <si>
+    <t>/storage/products/73.png</t>
+  </si>
+  <si>
     <t>Средство для стекол Mr.Green 'POWER' 500 мл</t>
   </si>
   <si>
+    <t>Универсальное концентрированное моющее средство для стекол...</t>
+  </si>
+  <si>
+    <t>/storage/products/74.png</t>
+  </si>
+  <si>
     <t>Средство для удаления засоров MR.GREEN TURBO MAX 500 мл</t>
   </si>
   <si>
+    <t>Средство для прочистки стоков и канализационных труб...</t>
+  </si>
+  <si>
+    <t>/storage/products/75.png</t>
+  </si>
+  <si>
     <t>MR.GREEN 'POWER' для Ванны 500 мл</t>
   </si>
   <si>
+    <t>Кислотное моющее средство для очистки раковин, унитазов...</t>
+  </si>
+  <si>
+    <t>/storage/products/76.png</t>
+  </si>
+  <si>
     <t>Средство для унитазов Mr.Green 'POWER' тройная сила кислотное 750 мл</t>
   </si>
   <si>
+    <t>/storage/products/77.png</t>
+  </si>
+  <si>
+    <t>750 мл</t>
+  </si>
+  <si>
     <t>Средство для унитазов Mr.Green 'POWER' тройная сила щелочное 750 мл</t>
   </si>
   <si>
+    <t>Легко удаляет налет и ржавчину...</t>
+  </si>
+  <si>
+    <t>/storage/products/78.png</t>
+  </si>
+  <si>
     <t>Средство для мытья полов MR.GREEN Bio system 1000 мл</t>
   </si>
   <si>
+    <t>Жидкий нейтральный концентрат с отличным обезжиривающим действием...</t>
+  </si>
+  <si>
+    <t>/storage/products/79.png</t>
+  </si>
+  <si>
+    <t>1000 мл</t>
+  </si>
+  <si>
     <t>Кондиционер для белья MR.GREEN Лаванда 1500 мл</t>
   </si>
   <si>
+    <t>Кондиционер для придания мягкости и свежести белью...</t>
+  </si>
+  <si>
+    <t>/storage/products/80.png</t>
+  </si>
+  <si>
+    <t>1500 мл</t>
+  </si>
+  <si>
     <t>Кондиционер для белья MR.GREEN Черника 1500 мл</t>
   </si>
   <si>
+    <t>/storage/products/81.png</t>
+  </si>
+  <si>
     <t>Кондиционер для белья MR.GREEN Нежность Хлопка 1500 мл</t>
   </si>
   <si>
+    <t>/storage/products/82.png</t>
+  </si>
+  <si>
     <t>Гель для стирки Mr.Green Color Deluxe 2000 мл</t>
   </si>
   <si>
+    <t>Гелеобразное моющее средство для стирки белья...</t>
+  </si>
+  <si>
+    <t>/storage/products/83.png</t>
+  </si>
+  <si>
+    <t>2000 мл</t>
+  </si>
+  <si>
     <t>Гель для стирки Mr.Green Color Deluxe 5000 мл</t>
   </si>
   <si>
+    <t>/storage/products/84.png</t>
+  </si>
+  <si>
+    <t>5000 мл</t>
+  </si>
+  <si>
     <t>Гель для стирки Mr.Green 'Альпийские луга' 2000 мл</t>
   </si>
   <si>
+    <t>/storage/products/85.png</t>
+  </si>
+  <si>
     <t>Гель для стирки Mr.Green 'Альпийские луга' 5000 мл</t>
   </si>
   <si>
+    <t>/storage/products/86.png</t>
+  </si>
+  <si>
     <t>MR.GREEN Средство от накипи для стиральных машин 500 мл</t>
   </si>
   <si>
+    <t>Средство эффективно в воде любой жесткости...</t>
+  </si>
+  <si>
+    <t>/storage/products/87.png</t>
+  </si>
+  <si>
     <t>Универсальное моющее средство MR.GREEN PROGRESSIVE ТИТАН 1000 мл</t>
   </si>
   <si>
-    <t>Гелеобразный нейтральный концентрат умеренной пенности...</t>
-  </si>
-  <si>
-    <t>Жидкий сильнощелочной концентрат для очистки от нагара...</t>
-  </si>
-  <si>
-    <t>Универсальное концентрированное моющее средство для стекол...</t>
-  </si>
-  <si>
-    <t>Средство для прочистки стоков и канализационных труб...</t>
-  </si>
-  <si>
-    <t>Кислотное моющее средство для очистки раковин, унитазов...</t>
-  </si>
-  <si>
-    <t>Легко удаляет налет и ржавчину...</t>
-  </si>
-  <si>
-    <t>Жидкий нейтральный концентрат с отличным обезжиривающим действием...</t>
-  </si>
-  <si>
-    <t>Кондиционер для придания мягкости и свежести белью...</t>
-  </si>
-  <si>
-    <t>Гелеобразное моющее средство для стирки белья...</t>
-  </si>
-  <si>
-    <t>Средство эффективно в воде любой жесткости...</t>
-  </si>
-  <si>
     <t>Универсальное моющее средство для мытья посуды и твердых поверхностей...</t>
   </si>
   <si>
-    <t>/storage/products/67.png</t>
-  </si>
-  <si>
-    <t>/storage/products/68.png</t>
-  </si>
-  <si>
-    <t>/storage/products/69.png</t>
-  </si>
-  <si>
-    <t>/storage/products/70.png</t>
-  </si>
-  <si>
-    <t>/storage/products/71.png</t>
-  </si>
-  <si>
-    <t>/storage/products/72.png</t>
-  </si>
-  <si>
-    <t>/storage/products/73.png</t>
-  </si>
-  <si>
-    <t>/storage/products/74.png</t>
-  </si>
-  <si>
-    <t>/storage/products/75.png</t>
-  </si>
-  <si>
-    <t>/storage/products/76.png</t>
-  </si>
-  <si>
-    <t>/storage/products/77.png</t>
-  </si>
-  <si>
-    <t>/storage/products/78.png</t>
-  </si>
-  <si>
-    <t>/storage/products/79.png</t>
-  </si>
-  <si>
-    <t>/storage/products/80.png</t>
-  </si>
-  <si>
-    <t>/storage/products/81.png</t>
-  </si>
-  <si>
-    <t>/storage/products/82.png</t>
-  </si>
-  <si>
-    <t>/storage/products/83.png</t>
-  </si>
-  <si>
-    <t>/storage/products/84.png</t>
-  </si>
-  <si>
-    <t>/storage/products/85.png</t>
-  </si>
-  <si>
-    <t>/storage/products/86.png</t>
-  </si>
-  <si>
-    <t>/storage/products/87.png</t>
-  </si>
-  <si>
     <t>/storage/products/88.png</t>
-  </si>
-  <si>
-    <t>1 шт</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -258,19 +298,356 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -293,21 +670,316 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -590,14 +1262,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:R23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="76" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
@@ -666,19 +1342,19 @@
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I2">
         <v>365</v>
@@ -687,10 +1363,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -707,22 +1383,22 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I3">
         <v>365</v>
@@ -731,10 +1407,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -751,22 +1427,22 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" t="s">
-        <v>41</v>
       </c>
       <c r="I4">
         <v>365</v>
@@ -775,10 +1451,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="L4" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -795,22 +1471,22 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I5">
         <v>365</v>
@@ -819,10 +1495,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="L5" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -839,22 +1515,22 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H6" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I6">
         <v>365</v>
@@ -863,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="L6" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -883,22 +1559,22 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I7">
         <v>365</v>
@@ -907,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L7" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -927,22 +1603,22 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I8">
         <v>620</v>
@@ -951,10 +1627,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L8" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -971,22 +1647,22 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I9">
         <v>580</v>
@@ -995,10 +1671,10 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="L9" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -1015,22 +1691,22 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I10">
         <v>690</v>
@@ -1039,10 +1715,10 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="L10" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -1059,13 +1735,13 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
         <v>45</v>
@@ -1083,10 +1759,10 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="L11" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -1103,13 +1779,13 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
         <v>45</v>
@@ -1127,10 +1803,10 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>62</v>
-      </c>
-      <c r="L12" t="s">
-        <v>74</v>
+        <v>48</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="Q12">
         <v>1</v>
@@ -1147,22 +1823,22 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G13" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H13" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I13">
         <v>575</v>
@@ -1171,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>63</v>
-      </c>
-      <c r="L13" t="s">
-        <v>74</v>
+        <v>52</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="Q13">
         <v>1</v>
@@ -1191,22 +1867,22 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G14" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H14" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I14">
         <v>760</v>
@@ -1215,10 +1891,10 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="L14" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1235,22 +1911,22 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G15" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H15" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="I15">
         <v>1080</v>
@@ -1259,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="L15" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="Q15">
         <v>1</v>
@@ -1279,22 +1955,22 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="F16" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G16" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="I16">
         <v>1080</v>
@@ -1303,10 +1979,10 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L16" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="Q16">
         <v>1</v>
@@ -1323,22 +1999,22 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G17" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="I17">
         <v>1080</v>
@@ -1347,10 +2023,10 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L17" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="Q17">
         <v>1</v>
@@ -1367,22 +2043,22 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G18" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="H18" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="I18">
         <v>1530</v>
@@ -1391,10 +2067,10 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
+        <v>67</v>
+      </c>
+      <c r="L18" t="s">
         <v>68</v>
-      </c>
-      <c r="L18" t="s">
-        <v>74</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -1411,22 +2087,22 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G19" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="I19">
         <v>3330</v>
@@ -1435,10 +2111,10 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q19">
         <v>1</v>
@@ -1455,22 +2131,22 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="F20" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G20" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="H20" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="I20">
         <v>1530</v>
@@ -1479,10 +2155,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L20" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="Q20">
         <v>1</v>
@@ -1499,22 +2175,22 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="H21" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="I21">
         <v>3330</v>
@@ -1523,10 +2199,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
+        <v>75</v>
+      </c>
+      <c r="L21" t="s">
         <v>71</v>
-      </c>
-      <c r="L21" t="s">
-        <v>74</v>
       </c>
       <c r="Q21">
         <v>1</v>
@@ -1543,22 +2219,22 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="E22" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="I22">
         <v>585</v>
@@ -1567,10 +2243,10 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L22" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="Q22">
         <v>1</v>
@@ -1587,22 +2263,22 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="I23">
         <v>400</v>
@@ -1611,10 +2287,10 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L23" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="Q23">
         <v>1</v>
@@ -1625,5 +2301,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/database/seeders/xlsx/2.xlsx
+++ b/database/seeders/xlsx/2.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="100">
   <si>
     <t>subcategory_id</t>
   </si>
@@ -110,30 +110,45 @@
     <t>/storage/products/68.png</t>
   </si>
   <si>
+    <t>Средство для мытья посуды MR.GREEN Яблоко</t>
+  </si>
+  <si>
     <t>Средство для мытья посуды MR.GREEN Яблоко 500 мл</t>
   </si>
   <si>
     <t>/storage/products/69.png</t>
   </si>
   <si>
+    <t>Средство для мытья посуды MR.GREEN Лимон</t>
+  </si>
+  <si>
     <t>Средство для мытья посуды MR.GREEN Лимон 500 мл</t>
   </si>
   <si>
     <t>/storage/products/70.png</t>
   </si>
   <si>
+    <t>Средство для мытья посуды MR.GREEN Гранат</t>
+  </si>
+  <si>
     <t>Средство для мытья посуды MR.GREEN Гранат 500 мл</t>
   </si>
   <si>
     <t>/storage/products/71.png</t>
   </si>
   <si>
+    <t>Средство для мытья посуды MR.GREEN Лайм-Мята</t>
+  </si>
+  <si>
     <t>Средство для мытья посуды MR.GREEN Лайм-Мята 500 мл</t>
   </si>
   <si>
     <t>/storage/products/72.png</t>
   </si>
   <si>
+    <t>MR.GREEN 'POWER' АНТИЖИР PROFESSIONAL</t>
+  </si>
+  <si>
     <t>MR.GREEN 'POWER' АНТИЖИР PROFESSIONAL 500 мл</t>
   </si>
   <si>
@@ -143,6 +158,9 @@
     <t>/storage/products/73.png</t>
   </si>
   <si>
+    <t>Средство для стекол Mr.Green 'POWER'</t>
+  </si>
+  <si>
     <t>Средство для стекол Mr.Green 'POWER' 500 мл</t>
   </si>
   <si>
@@ -152,6 +170,9 @@
     <t>/storage/products/74.png</t>
   </si>
   <si>
+    <t>Средство для удаления засоров MR.GREEN TURBO MAX</t>
+  </si>
+  <si>
     <t>Средство для удаления засоров MR.GREEN TURBO MAX 500 мл</t>
   </si>
   <si>
@@ -161,6 +182,9 @@
     <t>/storage/products/75.png</t>
   </si>
   <si>
+    <t>MR.GREEN 'POWER' для Ванны</t>
+  </si>
+  <si>
     <t>MR.GREEN 'POWER' для Ванны 500 мл</t>
   </si>
   <si>
@@ -170,6 +194,9 @@
     <t>/storage/products/76.png</t>
   </si>
   <si>
+    <t>Средство для унитазов Mr.Green 'POWER' тройная сила кислотное</t>
+  </si>
+  <si>
     <t>Средство для унитазов Mr.Green 'POWER' тройная сила кислотное 750 мл</t>
   </si>
   <si>
@@ -179,6 +206,9 @@
     <t>750 мл</t>
   </si>
   <si>
+    <t>Средство для унитазов Mr.Green 'POWER' тройная сила щелочное</t>
+  </si>
+  <si>
     <t>Средство для унитазов Mr.Green 'POWER' тройная сила щелочное 750 мл</t>
   </si>
   <si>
@@ -188,6 +218,9 @@
     <t>/storage/products/78.png</t>
   </si>
   <si>
+    <t>Средство для мытья полов MR.GREEN Bio system</t>
+  </si>
+  <si>
     <t>Средство для мытья полов MR.GREEN Bio system 1000 мл</t>
   </si>
   <si>
@@ -200,6 +233,9 @@
     <t>1000 мл</t>
   </si>
   <si>
+    <t>Кондиционер для белья MR.GREEN Лаванда</t>
+  </si>
+  <si>
     <t>Кондиционер для белья MR.GREEN Лаванда 1500 мл</t>
   </si>
   <si>
@@ -212,18 +248,27 @@
     <t>1500 мл</t>
   </si>
   <si>
+    <t>Кондиционер для белья MR.GREEN Черника</t>
+  </si>
+  <si>
     <t>Кондиционер для белья MR.GREEN Черника 1500 мл</t>
   </si>
   <si>
     <t>/storage/products/81.png</t>
   </si>
   <si>
+    <t>Кондиционер для белья MR.GREEN Нежность Хлопка</t>
+  </si>
+  <si>
     <t>Кондиционер для белья MR.GREEN Нежность Хлопка 1500 мл</t>
   </si>
   <si>
     <t>/storage/products/82.png</t>
   </si>
   <si>
+    <t>Гель для стирки Mr.Green Color Deluxe</t>
+  </si>
+  <si>
     <t>Гель для стирки Mr.Green Color Deluxe 2000 мл</t>
   </si>
   <si>
@@ -245,6 +290,9 @@
     <t>5000 мл</t>
   </si>
   <si>
+    <t xml:space="preserve">Гель для стирки Mr.Green 'Альпийские луга' </t>
+  </si>
+  <si>
     <t>Гель для стирки Mr.Green 'Альпийские луга' 2000 мл</t>
   </si>
   <si>
@@ -257,6 +305,9 @@
     <t>/storage/products/86.png</t>
   </si>
   <si>
+    <t>MR.GREEN Средство от накипи для стиральных машин</t>
+  </si>
+  <si>
     <t>MR.GREEN Средство от накипи для стиральных машин 500 мл</t>
   </si>
   <si>
@@ -264,6 +315,9 @@
   </si>
   <si>
     <t>/storage/products/87.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Универсальное моющее средство MR.GREEN PROGRESSIVE ТИТАН </t>
   </si>
   <si>
     <t>Универсальное моющее средство MR.GREEN PROGRESSIVE ТИТАН 1000 мл</t>
@@ -285,7 +339,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -295,13 +349,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -771,148 +818,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1430,10 +1477,10 @@
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
         <v>21</v>
@@ -1451,7 +1498,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L4" t="s">
         <v>23</v>
@@ -1471,13 +1518,13 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -1495,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L5" t="s">
         <v>23</v>
@@ -1515,13 +1562,13 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -1539,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L6" t="s">
         <v>23</v>
@@ -1559,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
         <v>21</v>
@@ -1583,7 +1630,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L7" t="s">
         <v>23</v>
@@ -1603,22 +1650,22 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I8">
         <v>620</v>
@@ -1627,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L8" t="s">
         <v>23</v>
@@ -1647,22 +1694,22 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I9">
         <v>580</v>
@@ -1671,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L9" t="s">
         <v>23</v>
@@ -1691,22 +1738,22 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H10" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I10">
         <v>690</v>
@@ -1715,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="L10" t="s">
         <v>23</v>
@@ -1735,22 +1782,22 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="I11">
         <v>930</v>
@@ -1759,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="L11" t="s">
         <v>23</v>
@@ -1779,22 +1826,22 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G12" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H12" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="I12">
         <v>495</v>
@@ -1803,10 +1850,10 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q12">
         <v>1</v>
@@ -1823,22 +1870,22 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H13" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I13">
         <v>575</v>
@@ -1847,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q13">
         <v>1</v>
@@ -1867,22 +1914,22 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G14" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="H14" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="I14">
         <v>760</v>
@@ -1891,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="L14" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1911,22 +1958,22 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H15" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="I15">
         <v>1080</v>
@@ -1935,10 +1982,10 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="L15" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="Q15">
         <v>1</v>
@@ -1955,22 +2002,22 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="G16" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H16" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="I16">
         <v>1080</v>
@@ -1979,10 +2026,10 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="L16" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="Q16">
         <v>1</v>
@@ -1999,22 +2046,22 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="G17" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="I17">
         <v>1080</v>
@@ -2023,10 +2070,10 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="L17" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="Q17">
         <v>1</v>
@@ -2043,22 +2090,22 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="I18">
         <v>1530</v>
@@ -2067,10 +2114,10 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="L18" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -2087,22 +2134,22 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="I19">
         <v>3330</v>
@@ -2111,10 +2158,10 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="L19" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="Q19">
         <v>1</v>
@@ -2131,22 +2178,22 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="I20">
         <v>1530</v>
@@ -2155,10 +2202,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="L20" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="Q20">
         <v>1</v>
@@ -2175,22 +2222,22 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="I21">
         <v>3330</v>
@@ -2199,10 +2246,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="L21" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="Q21">
         <v>1</v>
@@ -2219,22 +2266,22 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="I22">
         <v>585</v>
@@ -2243,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="L22" t="s">
         <v>23</v>
@@ -2263,22 +2310,22 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="G23" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="H23" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="I23">
         <v>400</v>
@@ -2287,10 +2334,10 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="L23" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="Q23">
         <v>1</v>

--- a/database/seeders/xlsx/2.xlsx
+++ b/database/seeders/xlsx/2.xlsx
@@ -95,7 +95,7 @@
     <t>Гелеобразный нейтральный концентрат умеренной пенности...</t>
   </si>
   <si>
-    <t>/storage/products/67.png</t>
+    <t>/storage/products/1.png</t>
   </si>
   <si>
     <t>500 мл</t>
@@ -107,7 +107,7 @@
     <t>Средство для мытья посуды MR.GREEN Арбуз 500 мл</t>
   </si>
   <si>
-    <t>/storage/products/68.png</t>
+    <t>/storage/products/2.png</t>
   </si>
   <si>
     <t>Средство для мытья посуды MR.GREEN Яблоко</t>
@@ -116,7 +116,7 @@
     <t>Средство для мытья посуды MR.GREEN Яблоко 500 мл</t>
   </si>
   <si>
-    <t>/storage/products/69.png</t>
+    <t>/storage/products/3.png</t>
   </si>
   <si>
     <t>Средство для мытья посуды MR.GREEN Лимон</t>
@@ -125,7 +125,7 @@
     <t>Средство для мытья посуды MR.GREEN Лимон 500 мл</t>
   </si>
   <si>
-    <t>/storage/products/70.png</t>
+    <t>/storage/products/4.png</t>
   </si>
   <si>
     <t>Средство для мытья посуды MR.GREEN Гранат</t>
@@ -134,7 +134,7 @@
     <t>Средство для мытья посуды MR.GREEN Гранат 500 мл</t>
   </si>
   <si>
-    <t>/storage/products/71.png</t>
+    <t>/storage/products/5.png</t>
   </si>
   <si>
     <t>Средство для мытья посуды MR.GREEN Лайм-Мята</t>
@@ -143,7 +143,7 @@
     <t>Средство для мытья посуды MR.GREEN Лайм-Мята 500 мл</t>
   </si>
   <si>
-    <t>/storage/products/72.png</t>
+    <t>/storage/products/6.png</t>
   </si>
   <si>
     <t>MR.GREEN 'POWER' АНТИЖИР PROFESSIONAL</t>
@@ -155,7 +155,7 @@
     <t>Жидкий сильнощелочной концентрат для очистки от нагара...</t>
   </si>
   <si>
-    <t>/storage/products/73.png</t>
+    <t>/storage/products/7.png</t>
   </si>
   <si>
     <t>Средство для стекол Mr.Green 'POWER'</t>
@@ -167,7 +167,7 @@
     <t>Универсальное концентрированное моющее средство для стекол...</t>
   </si>
   <si>
-    <t>/storage/products/74.png</t>
+    <t>/storage/products/8.png</t>
   </si>
   <si>
     <t>Средство для удаления засоров MR.GREEN TURBO MAX</t>
@@ -179,7 +179,7 @@
     <t>Средство для прочистки стоков и канализационных труб...</t>
   </si>
   <si>
-    <t>/storage/products/75.png</t>
+    <t>/storage/products/9.png</t>
   </si>
   <si>
     <t>MR.GREEN 'POWER' для Ванны</t>
@@ -191,7 +191,7 @@
     <t>Кислотное моющее средство для очистки раковин, унитазов...</t>
   </si>
   <si>
-    <t>/storage/products/76.png</t>
+    <t>/storage/products/10.png</t>
   </si>
   <si>
     <t>Средство для унитазов Mr.Green 'POWER' тройная сила кислотное</t>
@@ -200,7 +200,7 @@
     <t>Средство для унитазов Mr.Green 'POWER' тройная сила кислотное 750 мл</t>
   </si>
   <si>
-    <t>/storage/products/77.png</t>
+    <t>/storage/products/11.png</t>
   </si>
   <si>
     <t>750 мл</t>
@@ -215,7 +215,7 @@
     <t>Легко удаляет налет и ржавчину...</t>
   </si>
   <si>
-    <t>/storage/products/78.png</t>
+    <t>/storage/products/12.png</t>
   </si>
   <si>
     <t>Средство для мытья полов MR.GREEN Bio system</t>
@@ -227,7 +227,7 @@
     <t>Жидкий нейтральный концентрат с отличным обезжиривающим действием...</t>
   </si>
   <si>
-    <t>/storage/products/79.png</t>
+    <t>/storage/products/13.png</t>
   </si>
   <si>
     <t>1000 мл</t>
@@ -242,7 +242,7 @@
     <t>Кондиционер для придания мягкости и свежести белью...</t>
   </si>
   <si>
-    <t>/storage/products/80.png</t>
+    <t>/storage/products/14.png</t>
   </si>
   <si>
     <t>1500 мл</t>
@@ -254,7 +254,7 @@
     <t>Кондиционер для белья MR.GREEN Черника 1500 мл</t>
   </si>
   <si>
-    <t>/storage/products/81.png</t>
+    <t>/storage/products/15.png</t>
   </si>
   <si>
     <t>Кондиционер для белья MR.GREEN Нежность Хлопка</t>
@@ -263,7 +263,7 @@
     <t>Кондиционер для белья MR.GREEN Нежность Хлопка 1500 мл</t>
   </si>
   <si>
-    <t>/storage/products/82.png</t>
+    <t>/storage/products/16.png</t>
   </si>
   <si>
     <t>Гель для стирки Mr.Green Color Deluxe</t>
@@ -275,7 +275,7 @@
     <t>Гелеобразное моющее средство для стирки белья...</t>
   </si>
   <si>
-    <t>/storage/products/83.png</t>
+    <t>/storage/products/17.png</t>
   </si>
   <si>
     <t>2000 мл</t>
@@ -284,7 +284,7 @@
     <t>Гель для стирки Mr.Green Color Deluxe 5000 мл</t>
   </si>
   <si>
-    <t>/storage/products/84.png</t>
+    <t>/storage/products/18.png</t>
   </si>
   <si>
     <t>5000 мл</t>
@@ -296,13 +296,13 @@
     <t>Гель для стирки Mr.Green 'Альпийские луга' 2000 мл</t>
   </si>
   <si>
-    <t>/storage/products/85.png</t>
+    <t>/storage/products/19.png</t>
   </si>
   <si>
     <t>Гель для стирки Mr.Green 'Альпийские луга' 5000 мл</t>
   </si>
   <si>
-    <t>/storage/products/86.png</t>
+    <t>/storage/products/20.png</t>
   </si>
   <si>
     <t>MR.GREEN Средство от накипи для стиральных машин</t>
@@ -314,7 +314,7 @@
     <t>Средство эффективно в воде любой жесткости...</t>
   </si>
   <si>
-    <t>/storage/products/87.png</t>
+    <t>/storage/products/21.png</t>
   </si>
   <si>
     <t xml:space="preserve">Универсальное моющее средство MR.GREEN PROGRESSIVE ТИТАН </t>
@@ -326,7 +326,7 @@
     <t>Универсальное моющее средство для мытья посуды и твердых поверхностей...</t>
   </si>
   <si>
-    <t>/storage/products/88.png</t>
+    <t>/storage/products/22.png</t>
   </si>
 </sst>
 </file>
@@ -1320,6 +1320,7 @@
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="76" customWidth="1"/>
+    <col min="11" max="11" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
